--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2947-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2947-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BED29959-14B2-4314-9D3E-77F018EB400A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D65DFD5-8752-4760-A2A0-EAE5C034EA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9BC7B1EA-DCEB-454D-AA03-6C92772DC4FC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7DF5F6FF-9039-4547-BF53-38A26AD850E4}"/>
   </bookViews>
   <sheets>
     <sheet name="2947-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1493,20 +1493,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B84507-C2BE-4647-9DD3-0CE1B034B015}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A920F564-33CA-4149-A93D-4A19D81DBEE3}">
   <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="23" width="6.75" customWidth="1"/>
-    <col min="24" max="24" width="9.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="23" width="5.88671875" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1540,7 +1540,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1696,7 +1696,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="39">
         <v>2024</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>29</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="42"/>
       <c r="B9" s="42"/>
       <c r="C9" s="20" t="s">
@@ -2016,7 +2016,7 @@
       <c r="W9" s="48"/>
       <c r="X9" s="44"/>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2456,7 +2456,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2020</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2019</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
         <v>42</v>
       </c>
